--- a/artfynd/A 32329-2021 artfynd.xlsx
+++ b/artfynd/A 32329-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32329-2021 artfynd.xlsx
+++ b/artfynd/A 32329-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94973710</v>
+        <v>94973884</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,7 +722,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332576</v>
+        <v>332577</v>
       </c>
       <c r="R2" t="n">
         <v>6380968</v>
@@ -767,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två vuxna minst 2 juvenila</t>
+          <t>Kiande några gånger</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94973884</v>
+        <v>94973837</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,16 +800,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,14 +819,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>revir, ej häckning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -846,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332576.2288508569</v>
+        <v>332577</v>
       </c>
       <c r="R3" t="n">
-        <v>6380967.838466911</v>
+        <v>6380968</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,24 +869,14 @@
           <t>2021-07-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kiande några gånger</t>
+          <t>Två adulta och troligen en tredje bivråk (hann inte notera riktigt). Flygträning. Häckning troligen i närområdet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,57 +903,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96198038</v>
+        <v>94973710</v>
       </c>
       <c r="B4" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hede, Hl</t>
+          <t>S Bådamossen A 32329-2021, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332510.8546121633</v>
+        <v>332577</v>
       </c>
       <c r="R4" t="n">
-        <v>6380662.068868697</v>
+        <v>6380968</v>
       </c>
       <c r="S4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +980,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två vuxna minst 2 juvenila</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,15 +1005,126 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96198038</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hede, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>332511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6380663</v>
+      </c>
+      <c r="S5" t="n">
+        <v>90</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tölö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Liza Andersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Liza Andersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
